--- a/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CA32C1-592B-4117-B9F9-94DFBEFF0B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="117">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -229,12 +243,6 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10698894</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>795 Store Management (Zogop Dogegy (On Leave) (10185858))</t>
   </si>
   <si>
@@ -350,9 +358,6 @@
   </si>
   <si>
     <t>Test2</t>
-  </si>
-  <si>
-    <t>10698895</t>
   </si>
   <si>
     <t>795 Recruitment (Zosig Depazi (10280602))</t>
@@ -379,58 +384,58 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -442,19 +447,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,15 +490,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +521,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -882,9 +901,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BV3"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
@@ -958,7 +977,7 @@
     <col min="74" max="74" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:74" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" spans="1:74" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1182,223 +1201,219 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="H2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="I2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="J2" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="17">
+        <f t="shared" ref="K2:K3" ca="1" si="0">TODAY()-7</f>
+        <v>45785</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="N2" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="17">
-        <f t="shared" ref="K2:K3" si="0">TODAY()-7</f>
-        <v>45776</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="N2" s="18" t="s">
-        <v>81</v>
-      </c>
       <c r="O2" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P2" s="16">
         <v>1542</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R2" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="S2" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="T2" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="U2" s="22">
+        <f t="shared" ref="U2:U3" ca="1" si="1">TODAY()-31</f>
+        <v>45761</v>
+      </c>
+      <c r="V2" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="21" t="s">
+      <c r="W2" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="T2" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="U2" s="22">
-        <f t="shared" ref="U2:U3" si="1">TODAY()-31</f>
-        <v>45752</v>
-      </c>
-      <c r="V2" s="16" t="s">
+      <c r="X2" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W2" s="23" t="s">
+      <c r="Y2" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="X2" s="24" t="s">
+      <c r="Z2" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y2" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z2" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA2" s="25">
         <v>795</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC2" s="26">
         <v>40</v>
       </c>
       <c r="AD2" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF2" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG2" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AH2" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF2" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG2" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH2" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI2" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ2" s="17">
-        <f t="shared" ref="AJ2:AL3" si="2">TODAY()-31</f>
-        <v>45752</v>
+        <f t="shared" ref="AJ2:AL3" ca="1" si="2">TODAY()-31</f>
+        <v>45761</v>
       </c>
       <c r="AK2" s="17">
-        <f t="shared" si="2"/>
-        <v>45752</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45761</v>
       </c>
       <c r="AL2" s="17">
-        <f t="shared" si="2"/>
-        <v>45752</v>
-      </c>
-      <c r="AM2" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45761</v>
+      </c>
+      <c r="AM2" s="22" t="str">
         <f t="shared" ref="AM2:AM3" si="3">AF2</f>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AN2" s="16">
         <v>92</v>
       </c>
       <c r="AO2" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP2" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ2" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="AP2" s="24" t="s">
+      <c r="AR2" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="AQ2" s="24" t="s">
+      <c r="AS2" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU2" s="17">
+        <f t="shared" ref="AU2:AU3" ca="1" si="4">TODAY()+7</f>
+        <v>45799</v>
+      </c>
+      <c r="AV2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW2" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="AR2" s="19" t="s">
+      <c r="AX2" s="30">
+        <f t="array" aca="1" ref="AX2:AX3" ca="1">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
+        <v>4395871015030</v>
+      </c>
+      <c r="AY2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AS2" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT2" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU2" s="17">
-        <f t="shared" ref="AU2:AU3" si="4">TODAY()+7</f>
-        <v>45790</v>
-      </c>
-      <c r="AV2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW2" s="29" t="s">
+      <c r="AZ2" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AX2" s="30">
-        <f t="array" ref="AX2:AX3">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
-        <v>1201571380892</v>
-      </c>
-      <c r="AY2" s="17" t="s">
+      <c r="BA2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB2" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="AZ2" s="17" t="s">
+      <c r="BC2" s="30">
+        <f t="array" aca="1" ref="BC2:BC3" ca="1">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
+        <v>27131599</v>
+      </c>
+      <c r="BD2" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BE2" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="BA2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB2" s="29" t="s">
+      <c r="BF2" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="BC2" s="30">
-        <f t="array" ref="BC2:BC3">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
-        <v>40580357</v>
-      </c>
-      <c r="BD2" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE2" s="17" t="s">
+      <c r="BG2" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BH2" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BF2" s="19" t="s">
+      <c r="BI2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ2" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BG2" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BH2" s="13" t="s">
+      <c r="BK2" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL2" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ2" s="13" t="s">
+      <c r="BM2" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="BK2" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL2" s="13" t="s">
+      <c r="BN2" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="BM2" s="32" t="s">
+      <c r="BO2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="BN2" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP2" s="13" t="s">
-        <v>109</v>
-      </c>
       <c r="BQ2" s="13">
-        <f t="array" ref="BQ2:BQ3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>28305</v>
+        <f t="array" aca="1" ref="BQ2:BQ3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
+        <v>54696</v>
       </c>
       <c r="BR2" s="17">
         <v>44562</v>
@@ -1410,227 +1425,225 @@
         <v>44562</v>
       </c>
       <c r="BU2" s="22">
-        <f t="shared" ref="BU2:BU3" si="5">TODAY()+365</f>
-        <v>46148</v>
+        <f t="shared" ref="BU2:BU3" ca="1" si="5">TODAY()+365</f>
+        <v>46157</v>
       </c>
       <c r="BV2" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="3" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="E3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="G3" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="H3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>45785</v>
+      </c>
+      <c r="L3" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="I3" s="16" t="s">
+      <c r="M3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="N3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="17">
-        <f t="shared" si="0"/>
-        <v>45776</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="N3" s="18" t="s">
-        <v>81</v>
-      </c>
       <c r="O3" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P3" s="16">
         <v>1542</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R3" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="U3" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>45761</v>
+      </c>
+      <c r="V3" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="S3" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="U3" s="22">
-        <f t="shared" si="1"/>
-        <v>45752</v>
-      </c>
-      <c r="V3" s="16" t="s">
+      <c r="W3" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="X3" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W3" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" s="24" t="s">
+      <c r="Y3" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z3" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y3" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z3" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA3" s="25">
         <v>795</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC3" s="26">
         <v>40</v>
       </c>
       <c r="AD3" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE3" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG3" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE3" s="19" t="s">
+      <c r="AH3" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF3" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG3" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH3" s="16" t="s">
+      <c r="AI3" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ3" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45761</v>
+      </c>
+      <c r="AK3" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45761</v>
+      </c>
+      <c r="AL3" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45761</v>
+      </c>
+      <c r="AM3" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v>N/A</v>
+      </c>
+      <c r="AN3" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO3" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="AP3" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="AI3" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ3" s="17">
-        <f t="shared" si="2"/>
-        <v>45752</v>
-      </c>
-      <c r="AK3" s="17">
-        <f t="shared" si="2"/>
-        <v>45752</v>
-      </c>
-      <c r="AL3" s="17">
-        <f t="shared" si="2"/>
-        <v>45752</v>
-      </c>
-      <c r="AM3" s="22">
-        <f t="shared" si="3"/>
-        <v>NaN</v>
-      </c>
-      <c r="AN3" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="AO3" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="AP3" s="24" t="s">
+      <c r="AQ3" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR3" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="AQ3" s="24" t="s">
+      <c r="AS3" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT3" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU3" s="17">
+        <f t="shared" ca="1" si="4"/>
+        <v>45799</v>
+      </c>
+      <c r="AV3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW3" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="AR3" s="19" t="s">
+      <c r="AX3" s="30">
+        <f ca="1"/>
+        <v>7329688276318</v>
+      </c>
+      <c r="AY3" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AS3" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT3" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU3" s="17">
-        <f t="shared" si="4"/>
-        <v>45790</v>
-      </c>
-      <c r="AV3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW3" s="29" t="s">
+      <c r="AZ3" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AX3" s="30">
-        <v>3266911361957</v>
-      </c>
-      <c r="AY3" s="17" t="s">
+      <c r="BA3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB3" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="AZ3" s="17" t="s">
+      <c r="BC3" s="30">
+        <f ca="1"/>
+        <v>84265107</v>
+      </c>
+      <c r="BD3" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BE3" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="BA3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB3" s="29" t="s">
+      <c r="BF3" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="BC3" s="30">
-        <v>25989337</v>
-      </c>
-      <c r="BD3" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE3" s="17" t="s">
+      <c r="BG3" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BH3" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BI3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ3" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BG3" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BH3" s="13" t="s">
+      <c r="BK3" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL3" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BI3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ3" s="13" t="s">
+      <c r="BM3" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="BK3" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL3" s="13" t="s">
+      <c r="BN3" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="BM3" s="32" t="s">
+      <c r="BO3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP3" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="BN3" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP3" s="13" t="s">
-        <v>109</v>
-      </c>
       <c r="BQ3" s="13">
-        <v>32281</v>
+        <f ca="1"/>
+        <v>40793</v>
       </c>
       <c r="BR3" s="17">
         <v>44562</v>
@@ -1642,40 +1655,25 @@
         <v>44562</v>
       </c>
       <c r="BU3" s="22">
-        <f t="shared" si="5"/>
-        <v>46148</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46157</v>
       </c>
       <c r="BV3" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH3 V2:V3 T2:T3 Q2:Q3 J2:J3 BL2:BL3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1"/>
-    <hyperlink ref="S3" r:id="rId2"/>
+    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CA32C1-592B-4117-B9F9-94DFBEFF0B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="121">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -243,16 +229,22 @@
     <t>Test1</t>
   </si>
   <si>
+    <t>10699092</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>795 Store Management (Zogop Dogegy (On Leave) (10185858))</t>
   </si>
   <si>
     <t>Slovenia</t>
   </si>
   <si>
-    <t>Jaqueline</t>
-  </si>
-  <si>
-    <t>Haag</t>
+    <t>Ettie</t>
+  </si>
+  <si>
+    <t>Toy</t>
   </si>
   <si>
     <t xml:space="preserve">070-417-626 </t>
@@ -279,7 +271,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 84185324</t>
+    <t>Auto 28684654</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -360,13 +352,26 @@
     <t>Test2</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Lonnie Fahey-Kozey' Employee:{10699093}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByRole('button', { name: 'Approve' })[22m
+[2m  -   locator resolved to &lt;button type="button" tabindex="-2" title="Approve" aria…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  - element was detached from the DOM, retrying[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>795 Recruitment (Zosig Depazi (10280602))</t>
   </si>
   <si>
-    <t>Eladio</t>
-  </si>
-  <si>
-    <t>Shanahan</t>
+    <t>Lonnie</t>
+  </si>
+  <si>
+    <t>Fahey-Kozey</t>
   </si>
   <si>
     <t>No</t>
@@ -384,58 +389,58 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -447,19 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -471,7 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -490,27 +495,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -521,9 +514,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -901,9 +892,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BV3"/>
-  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
@@ -977,7 +968,7 @@
     <col min="74" max="74" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:74" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1201,218 +1192,222 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
+      <c r="B2" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>72</v>
+      </c>
       <c r="D2" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="17">
+        <f t="shared" ref="K2:K3" si="0">TODAY()-7</f>
+        <v>45785</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K2" s="17">
-        <f t="shared" ref="K2:K3" ca="1" si="0">TODAY()-7</f>
-        <v>45785</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>72</v>
-      </c>
       <c r="M2" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N2" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O2" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P2" s="16">
         <v>1542</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R2" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S2" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U2" s="22">
-        <f t="shared" ref="U2:U3" ca="1" si="1">TODAY()-31</f>
+        <f t="shared" ref="U2:U3" si="1">TODAY()-31</f>
         <v>45761</v>
       </c>
       <c r="V2" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W2" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="X2" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y2" s="24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Z2" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA2" s="25">
         <v>795</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC2" s="26">
         <v>40</v>
       </c>
       <c r="AD2" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE2" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF2" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG2" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH2" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI2" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AH2" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI2" s="16" t="s">
-        <v>88</v>
-      </c>
       <c r="AJ2" s="17">
-        <f t="shared" ref="AJ2:AL3" ca="1" si="2">TODAY()-31</f>
+        <f t="shared" ref="AJ2:AL3" si="2">TODAY()-31</f>
         <v>45761</v>
       </c>
       <c r="AK2" s="17">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45761</v>
       </c>
       <c r="AL2" s="17">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45761</v>
       </c>
-      <c r="AM2" s="22" t="str">
+      <c r="AM2" s="22">
         <f t="shared" ref="AM2:AM3" si="3">AF2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AN2" s="16">
         <v>92</v>
       </c>
       <c r="AO2" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AP2" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AQ2" s="24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR2" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AS2" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT2" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU2" s="17">
-        <f t="shared" ref="AU2:AU3" ca="1" si="4">TODAY()+7</f>
+        <f t="shared" ref="AU2:AU3" si="4">TODAY()+7</f>
         <v>45799</v>
       </c>
       <c r="AV2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW2" s="29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AX2" s="30">
-        <f t="array" aca="1" ref="AX2:AX3" ca="1">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
+        <f t="array" ref="AX2:AX3">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
         <v>4395871015030</v>
       </c>
       <c r="AY2" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AZ2" s="17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BA2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB2" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC2" s="30">
+        <f t="array" ref="BC2:BC3">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
+        <v>27131599</v>
+      </c>
+      <c r="BD2" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BC2" s="30">
-        <f t="array" aca="1" ref="BC2:BC3" ca="1">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
-        <v>27131599</v>
-      </c>
-      <c r="BD2" s="17" t="s">
-        <v>97</v>
-      </c>
       <c r="BE2" s="17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BF2" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BG2" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BH2" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BI2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ2" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BK2" s="31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL2" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BM2" s="32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BN2" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BO2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP2" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BQ2" s="13">
-        <f t="array" aca="1" ref="BQ2:BQ3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
+        <f t="array" ref="BQ2:BQ3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
         <v>54696</v>
       </c>
       <c r="BR2" s="17">
@@ -1425,224 +1420,226 @@
         <v>44562</v>
       </c>
       <c r="BU2" s="22">
-        <f t="shared" ref="BU2:BU3" ca="1" si="5">TODAY()+365</f>
+        <f t="shared" ref="BU2:BU3" si="5">TODAY()+365</f>
         <v>46157</v>
       </c>
       <c r="BV2" s="16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="11"/>
+        <v>111</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>113</v>
+      </c>
       <c r="D3" s="12" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K3" s="17">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45785</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P3" s="16">
         <v>1542</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R3" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U3" s="22">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45761</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W3" s="23" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="X3" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y3" s="24" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Z3" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA3" s="25">
         <v>795</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC3" s="26">
         <v>40</v>
       </c>
       <c r="AD3" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE3" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF3" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG3" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH3" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI3" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AH3" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI3" s="16" t="s">
-        <v>88</v>
-      </c>
       <c r="AJ3" s="17">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45761</v>
       </c>
       <c r="AK3" s="17">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45761</v>
       </c>
       <c r="AL3" s="17">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45761</v>
       </c>
-      <c r="AM3" s="22" t="str">
+      <c r="AM3" s="22">
         <f t="shared" si="3"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AN3" s="16" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AO3" s="24" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AP3" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AQ3" s="24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR3" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT3" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU3" s="17">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45799</v>
       </c>
       <c r="AV3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW3" s="29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AX3" s="30">
-        <f ca="1"/>
         <v>7329688276318</v>
       </c>
       <c r="AY3" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AZ3" s="17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BA3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB3" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC3" s="30">
+        <v>84265107</v>
+      </c>
+      <c r="BD3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BC3" s="30">
-        <f ca="1"/>
-        <v>84265107</v>
-      </c>
-      <c r="BD3" s="17" t="s">
-        <v>97</v>
-      </c>
       <c r="BE3" s="17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BF3" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BG3" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BH3" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BI3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ3" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BK3" s="31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL3" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BM3" s="32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BN3" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BO3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP3" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BQ3" s="13">
-        <f ca="1"/>
         <v>40793</v>
       </c>
       <c r="BR3" s="17">
@@ -1655,25 +1652,40 @@
         <v>44562</v>
       </c>
       <c r="BU3" s="22">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>46157</v>
       </c>
       <c r="BV3" s="16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH3 V2:V3 T2:T3 Q2:Q3 J2:J3 BL2:BL3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="S2" r:id="rId1"/>
+    <hyperlink ref="S3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{FA36E95B-8289-4EA3-882C-FA08A50A18DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="117">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -229,22 +244,16 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10698894</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>795 Store Management (Zogop Dogegy (On Leave) (10185858))</t>
   </si>
   <si>
     <t>Slovenia</t>
   </si>
   <si>
-    <t>Jaqueline</t>
-  </si>
-  <si>
-    <t>Haag</t>
+    <t>Josiane</t>
+  </si>
+  <si>
+    <t>Swift</t>
   </si>
   <si>
     <t xml:space="preserve">070-417-626 </t>
@@ -271,7 +280,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 84185324</t>
+    <t>Auto 32128790</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -352,16 +361,13 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10698895</t>
-  </si>
-  <si>
     <t>795 Recruitment (Zosig Depazi (10280602))</t>
   </si>
   <si>
-    <t>Eladio</t>
-  </si>
-  <si>
-    <t>Shanahan</t>
+    <t>Tyrese</t>
+  </si>
+  <si>
+    <t>Ortiz</t>
   </si>
   <si>
     <t>No</t>
@@ -379,58 +385,58 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -442,19 +448,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -466,7 +472,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -485,15 +491,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +522,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -882,11 +902,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BV3"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="59.6328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.90625" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.54296875" style="1" customWidth="1"/>
@@ -958,7 +979,7 @@
     <col min="74" max="74" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:74" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" spans="1:74" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1182,223 +1203,219 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="H2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="I2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="J2" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="17">
+        <f t="shared" ref="K2:K3" ca="1" si="0">TODAY()-7</f>
+        <v>45798</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="N2" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="17">
-        <f t="shared" ref="K2:K3" si="0">TODAY()-7</f>
-        <v>45776</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="N2" s="18" t="s">
-        <v>81</v>
-      </c>
       <c r="O2" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P2" s="16">
         <v>1542</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R2" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="S2" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="T2" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="U2" s="22">
+        <f t="shared" ref="U2:U3" ca="1" si="1">TODAY()-31</f>
+        <v>45774</v>
+      </c>
+      <c r="V2" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="21" t="s">
+      <c r="W2" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="T2" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="U2" s="22">
-        <f t="shared" ref="U2:U3" si="1">TODAY()-31</f>
-        <v>45752</v>
-      </c>
-      <c r="V2" s="16" t="s">
+      <c r="X2" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W2" s="23" t="s">
+      <c r="Y2" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="X2" s="24" t="s">
+      <c r="Z2" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y2" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z2" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA2" s="25">
         <v>795</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC2" s="26">
         <v>40</v>
       </c>
       <c r="AD2" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF2" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG2" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AH2" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF2" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG2" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH2" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI2" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ2" s="17">
-        <f t="shared" ref="AJ2:AL3" si="2">TODAY()-31</f>
-        <v>45752</v>
+        <f t="shared" ref="AJ2:AL3" ca="1" si="2">TODAY()-31</f>
+        <v>45774</v>
       </c>
       <c r="AK2" s="17">
-        <f t="shared" si="2"/>
-        <v>45752</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45774</v>
       </c>
       <c r="AL2" s="17">
-        <f t="shared" si="2"/>
-        <v>45752</v>
-      </c>
-      <c r="AM2" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45774</v>
+      </c>
+      <c r="AM2" s="22" t="str">
         <f t="shared" ref="AM2:AM3" si="3">AF2</f>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AN2" s="16">
         <v>92</v>
       </c>
       <c r="AO2" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP2" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ2" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="AP2" s="24" t="s">
+      <c r="AR2" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="AQ2" s="24" t="s">
+      <c r="AS2" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU2" s="17">
+        <f t="shared" ref="AU2:AU3" ca="1" si="4">TODAY()+7</f>
+        <v>45812</v>
+      </c>
+      <c r="AV2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW2" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="AR2" s="19" t="s">
+      <c r="AX2" s="30">
+        <f t="array" aca="1" ref="AX2:AX3" ca="1">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
+        <v>8913967594307</v>
+      </c>
+      <c r="AY2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AS2" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT2" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU2" s="17">
-        <f t="shared" ref="AU2:AU3" si="4">TODAY()+7</f>
-        <v>45790</v>
-      </c>
-      <c r="AV2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW2" s="29" t="s">
+      <c r="AZ2" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AX2" s="30">
-        <f t="array" ref="AX2:AX3">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
-        <v>1201571380892</v>
-      </c>
-      <c r="AY2" s="17" t="s">
+      <c r="BA2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB2" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="AZ2" s="17" t="s">
+      <c r="BC2" s="30">
+        <f t="array" aca="1" ref="BC2:BC3" ca="1">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
+        <v>31725942</v>
+      </c>
+      <c r="BD2" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BE2" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="BA2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB2" s="29" t="s">
+      <c r="BF2" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="BC2" s="30">
-        <f t="array" ref="BC2:BC3">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
-        <v>40580357</v>
-      </c>
-      <c r="BD2" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE2" s="17" t="s">
+      <c r="BG2" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BH2" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BF2" s="19" t="s">
+      <c r="BI2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ2" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BG2" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BH2" s="13" t="s">
+      <c r="BK2" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL2" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ2" s="13" t="s">
+      <c r="BM2" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="BK2" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL2" s="13" t="s">
+      <c r="BN2" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="BM2" s="32" t="s">
+      <c r="BO2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="BN2" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP2" s="13" t="s">
-        <v>109</v>
-      </c>
       <c r="BQ2" s="13">
-        <f t="array" ref="BQ2:BQ3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>28305</v>
+        <f t="array" aca="1" ref="BQ2:BQ3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
+        <v>76790</v>
       </c>
       <c r="BR2" s="17">
         <v>44562</v>
@@ -1410,227 +1427,226 @@
         <v>44562</v>
       </c>
       <c r="BU2" s="22">
-        <f t="shared" ref="BU2:BU3" si="5">TODAY()+365</f>
-        <v>46148</v>
+        <f t="shared" ref="BU2:BU3" ca="1" si="5">TODAY()+365</f>
+        <v>46170</v>
       </c>
       <c r="BV2" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="3" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="E3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="G3" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="H3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>45798</v>
+      </c>
+      <c r="L3" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="I3" s="16" t="s">
+      <c r="M3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="N3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="17">
-        <f t="shared" si="0"/>
-        <v>45776</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="N3" s="18" t="s">
-        <v>81</v>
-      </c>
       <c r="O3" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P3" s="16">
         <v>1542</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R3" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="U3" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>45774</v>
+      </c>
+      <c r="V3" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="S3" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="U3" s="22">
-        <f t="shared" si="1"/>
-        <v>45752</v>
-      </c>
-      <c r="V3" s="16" t="s">
+      <c r="W3" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="X3" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W3" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" s="24" t="s">
+      <c r="Y3" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z3" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y3" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z3" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA3" s="25">
         <v>795</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC3" s="26">
         <v>40</v>
       </c>
       <c r="AD3" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE3" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG3" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE3" s="19" t="s">
+      <c r="AH3" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF3" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG3" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH3" s="16" t="s">
+      <c r="AI3" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ3" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45774</v>
+      </c>
+      <c r="AK3" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45774</v>
+      </c>
+      <c r="AL3" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45774</v>
+      </c>
+      <c r="AM3" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v>N/A</v>
+      </c>
+      <c r="AN3" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO3" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="AP3" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="AI3" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ3" s="17">
-        <f t="shared" si="2"/>
-        <v>45752</v>
-      </c>
-      <c r="AK3" s="17">
-        <f t="shared" si="2"/>
-        <v>45752</v>
-      </c>
-      <c r="AL3" s="17">
-        <f t="shared" si="2"/>
-        <v>45752</v>
-      </c>
-      <c r="AM3" s="22">
-        <f t="shared" si="3"/>
-        <v>NaN</v>
-      </c>
-      <c r="AN3" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="AO3" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="AP3" s="24" t="s">
+      <c r="AQ3" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR3" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="AQ3" s="24" t="s">
+      <c r="AS3" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT3" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU3" s="17">
+        <f t="shared" ca="1" si="4"/>
+        <v>45812</v>
+      </c>
+      <c r="AV3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW3" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="AR3" s="19" t="s">
+      <c r="AX3" s="30">
+        <f ca="1"/>
+        <v>5484172821085</v>
+      </c>
+      <c r="AY3" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AS3" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT3" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU3" s="17">
-        <f t="shared" si="4"/>
-        <v>45790</v>
-      </c>
-      <c r="AV3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW3" s="29" t="s">
+      <c r="AZ3" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AX3" s="30">
-        <v>3266911361957</v>
-      </c>
-      <c r="AY3" s="17" t="s">
+      <c r="BA3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB3" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="AZ3" s="17" t="s">
+      <c r="BC3" s="30">
+        <f ca="1"/>
+        <v>91401970</v>
+      </c>
+      <c r="BD3" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BE3" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="BA3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB3" s="29" t="s">
+      <c r="BF3" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="BC3" s="30">
-        <v>25989337</v>
-      </c>
-      <c r="BD3" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE3" s="17" t="s">
+      <c r="BG3" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BH3" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BI3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ3" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BG3" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BH3" s="13" t="s">
+      <c r="BK3" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL3" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BI3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ3" s="13" t="s">
+      <c r="BM3" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="BK3" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL3" s="13" t="s">
+      <c r="BN3" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="BM3" s="32" t="s">
+      <c r="BO3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP3" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="BN3" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP3" s="13" t="s">
-        <v>109</v>
-      </c>
       <c r="BQ3" s="13">
-        <v>32281</v>
+        <f ca="1"/>
+        <v>88365</v>
       </c>
       <c r="BR3" s="17">
         <v>44562</v>
@@ -1642,40 +1658,25 @@
         <v>44562</v>
       </c>
       <c r="BU3" s="22">
-        <f t="shared" si="5"/>
-        <v>46148</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46170</v>
       </c>
       <c r="BV3" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH3 V2:V3 T2:T3 Q2:Q3 J2:J3 BL2:BL3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1"/>
-    <hyperlink ref="S3" r:id="rId2"/>
+    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="120">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -229,7 +229,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699092</t>
+    <t>10699541</t>
   </si>
   <si>
     <t>Passed</t>
@@ -241,10 +241,10 @@
     <t>Slovenia</t>
   </si>
   <si>
-    <t>Ettie</t>
-  </si>
-  <si>
-    <t>Toy</t>
+    <t>Treva</t>
+  </si>
+  <si>
+    <t>Rodriguez</t>
   </si>
   <si>
     <t xml:space="preserve">070-417-626 </t>
@@ -271,7 +271,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 28684654</t>
+    <t>Auto 56587565</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -352,26 +352,16 @@
     <t>Test2</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Lonnie Fahey-Kozey' Employee:{10699093}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByRole('button', { name: 'Approve' })[22m
-[2m  -   locator resolved to &lt;button type="button" tabindex="-2" title="Approve" aria…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  - element was detached from the DOM, retrying[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
+    <t>10699542</t>
   </si>
   <si>
     <t>795 Recruitment (Zosig Depazi (10280602))</t>
   </si>
   <si>
-    <t>Lonnie</t>
-  </si>
-  <si>
-    <t>Fahey-Kozey</t>
+    <t>Reece</t>
+  </si>
+  <si>
+    <t>Hahn</t>
   </si>
   <si>
     <t>No</t>
@@ -476,7 +466,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -1225,7 +1215,7 @@
       </c>
       <c r="K2" s="17">
         <f t="shared" ref="K2:K3" si="0">TODAY()-7</f>
-        <v>45785</v>
+        <v>45803</v>
       </c>
       <c r="L2" s="13" t="s">
         <v>74</v>
@@ -1256,7 +1246,7 @@
       </c>
       <c r="U2" s="22">
         <f t="shared" ref="U2:U3" si="1">TODAY()-31</f>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="V2" s="16" t="s">
         <v>84</v>
@@ -1302,15 +1292,15 @@
       </c>
       <c r="AJ2" s="17">
         <f t="shared" ref="AJ2:AL3" si="2">TODAY()-31</f>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AK2" s="17">
         <f t="shared" si="2"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AL2" s="17">
         <f t="shared" si="2"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AM2" s="22">
         <f t="shared" ref="AM2:AM3" si="3">AF2</f>
@@ -1339,7 +1329,7 @@
       </c>
       <c r="AU2" s="17">
         <f t="shared" ref="AU2:AU3" si="4">TODAY()+7</f>
-        <v>45799</v>
+        <v>45817</v>
       </c>
       <c r="AV2" s="13" t="s">
         <v>74</v>
@@ -1349,7 +1339,7 @@
       </c>
       <c r="AX2" s="30">
         <f t="array" ref="AX2:AX3">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
-        <v>4395871015030</v>
+        <v>4936340450811</v>
       </c>
       <c r="AY2" s="17" t="s">
         <v>99</v>
@@ -1365,7 +1355,7 @@
       </c>
       <c r="BC2" s="30">
         <f t="array" ref="BC2:BC3">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
-        <v>27131599</v>
+        <v>60089031</v>
       </c>
       <c r="BD2" s="17" t="s">
         <v>99</v>
@@ -1408,7 +1398,7 @@
       </c>
       <c r="BQ2" s="13">
         <f t="array" ref="BQ2:BQ3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>54696</v>
+        <v>87049</v>
       </c>
       <c r="BR2" s="17">
         <v>44562</v>
@@ -1421,7 +1411,7 @@
       </c>
       <c r="BU2" s="22">
         <f t="shared" ref="BU2:BU3" si="5">TODAY()+365</f>
-        <v>46157</v>
+        <v>46175</v>
       </c>
       <c r="BV2" s="16" t="s">
         <v>110</v>
@@ -1431,23 +1421,23 @@
       <c r="A3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="10" t="s">
         <v>112</v>
       </c>
       <c r="C3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>114</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>74</v>
       </c>
       <c r="F3" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>116</v>
       </c>
       <c r="H3" s="15" t="s">
         <v>77</v>
@@ -1460,7 +1450,7 @@
       </c>
       <c r="K3" s="17">
         <f t="shared" si="0"/>
-        <v>45785</v>
+        <v>45803</v>
       </c>
       <c r="L3" s="13" t="s">
         <v>74</v>
@@ -1491,19 +1481,19 @@
       </c>
       <c r="U3" s="22">
         <f t="shared" si="1"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="V3" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W3" s="23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X3" s="24" t="s">
         <v>86</v>
       </c>
       <c r="Y3" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z3" s="24" t="s">
         <v>88</v>
@@ -1537,25 +1527,25 @@
       </c>
       <c r="AJ3" s="17">
         <f t="shared" si="2"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AK3" s="17">
         <f t="shared" si="2"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AL3" s="17">
         <f t="shared" si="2"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AM3" s="22">
         <f t="shared" si="3"/>
         <v>NaN</v>
       </c>
       <c r="AN3" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO3" s="24" t="s">
         <v>119</v>
-      </c>
-      <c r="AO3" s="24" t="s">
-        <v>120</v>
       </c>
       <c r="AP3" s="24" t="s">
         <v>95</v>
@@ -1574,7 +1564,7 @@
       </c>
       <c r="AU3" s="17">
         <f t="shared" si="4"/>
-        <v>45799</v>
+        <v>45817</v>
       </c>
       <c r="AV3" s="13" t="s">
         <v>74</v>
@@ -1583,7 +1573,7 @@
         <v>98</v>
       </c>
       <c r="AX3" s="30">
-        <v>7329688276318</v>
+        <v>7964564254808</v>
       </c>
       <c r="AY3" s="17" t="s">
         <v>99</v>
@@ -1598,7 +1588,7 @@
         <v>101</v>
       </c>
       <c r="BC3" s="30">
-        <v>84265107</v>
+        <v>76302130</v>
       </c>
       <c r="BD3" s="17" t="s">
         <v>99</v>
@@ -1640,7 +1630,7 @@
         <v>109</v>
       </c>
       <c r="BQ3" s="13">
-        <v>40793</v>
+        <v>18270</v>
       </c>
       <c r="BR3" s="17">
         <v>44562</v>
@@ -1653,7 +1643,7 @@
       </c>
       <c r="BU3" s="22">
         <f t="shared" si="5"/>
-        <v>46157</v>
+        <v>46175</v>
       </c>
       <c r="BV3" s="16" t="s">
         <v>110</v>

--- a/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{BB2F1E8F-AB75-4EA2-85C3-7C1C0F36ABDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="117">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -229,12 +244,6 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699541</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>795 Store Management (Zogop Dogegy (On Leave) (10185858))</t>
   </si>
   <si>
@@ -350,9 +359,6 @@
   </si>
   <si>
     <t>Test2</t>
-  </si>
-  <si>
-    <t>10699542</t>
   </si>
   <si>
     <t>795 Recruitment (Zosig Depazi (10280602))</t>
@@ -379,58 +385,58 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -442,19 +448,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,15 +491,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +522,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -882,9 +902,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BV3"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
@@ -958,7 +978,7 @@
     <col min="74" max="74" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:74" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" spans="1:74" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1182,223 +1202,219 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="H2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="I2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="J2" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="17">
+        <f t="shared" ref="K2:K3" ca="1" si="0">TODAY()-7</f>
+        <v>45810</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="N2" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="17">
-        <f t="shared" ref="K2:K3" si="0">TODAY()-7</f>
-        <v>45803</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="N2" s="18" t="s">
-        <v>81</v>
-      </c>
       <c r="O2" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P2" s="16">
         <v>1542</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R2" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="S2" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="T2" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="U2" s="22">
+        <f t="shared" ref="U2:U3" ca="1" si="1">TODAY()-31</f>
+        <v>45786</v>
+      </c>
+      <c r="V2" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="21" t="s">
+      <c r="W2" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="T2" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="U2" s="22">
-        <f t="shared" ref="U2:U3" si="1">TODAY()-31</f>
-        <v>45779</v>
-      </c>
-      <c r="V2" s="16" t="s">
+      <c r="X2" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W2" s="23" t="s">
+      <c r="Y2" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="X2" s="24" t="s">
+      <c r="Z2" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y2" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z2" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA2" s="25">
         <v>795</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC2" s="26">
         <v>40</v>
       </c>
       <c r="AD2" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF2" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG2" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AH2" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF2" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG2" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH2" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI2" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ2" s="17">
-        <f t="shared" ref="AJ2:AL3" si="2">TODAY()-31</f>
-        <v>45779</v>
+        <f t="shared" ref="AJ2:AL3" ca="1" si="2">TODAY()-31</f>
+        <v>45786</v>
       </c>
       <c r="AK2" s="17">
-        <f t="shared" si="2"/>
-        <v>45779</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45786</v>
       </c>
       <c r="AL2" s="17">
-        <f t="shared" si="2"/>
-        <v>45779</v>
-      </c>
-      <c r="AM2" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45786</v>
+      </c>
+      <c r="AM2" s="22" t="str">
         <f t="shared" ref="AM2:AM3" si="3">AF2</f>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AN2" s="16">
         <v>92</v>
       </c>
       <c r="AO2" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP2" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ2" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="AP2" s="24" t="s">
+      <c r="AR2" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="AQ2" s="24" t="s">
+      <c r="AS2" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU2" s="17">
+        <f t="shared" ref="AU2:AU3" ca="1" si="4">TODAY()+7</f>
+        <v>45824</v>
+      </c>
+      <c r="AV2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW2" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="AR2" s="19" t="s">
+      <c r="AX2" s="30">
+        <f t="array" aca="1" ref="AX2:AX3" ca="1">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
+        <v>8140712665871</v>
+      </c>
+      <c r="AY2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AS2" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT2" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU2" s="17">
-        <f t="shared" ref="AU2:AU3" si="4">TODAY()+7</f>
-        <v>45817</v>
-      </c>
-      <c r="AV2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW2" s="29" t="s">
+      <c r="AZ2" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AX2" s="30">
-        <f t="array" ref="AX2:AX3">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
-        <v>4936340450811</v>
-      </c>
-      <c r="AY2" s="17" t="s">
+      <c r="BA2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB2" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="AZ2" s="17" t="s">
+      <c r="BC2" s="30">
+        <f t="array" aca="1" ref="BC2:BC3" ca="1">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
+        <v>33531089</v>
+      </c>
+      <c r="BD2" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BE2" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="BA2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB2" s="29" t="s">
+      <c r="BF2" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="BC2" s="30">
-        <f t="array" ref="BC2:BC3">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
-        <v>60089031</v>
-      </c>
-      <c r="BD2" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE2" s="17" t="s">
+      <c r="BG2" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BH2" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BF2" s="19" t="s">
+      <c r="BI2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ2" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BG2" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BH2" s="13" t="s">
+      <c r="BK2" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL2" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ2" s="13" t="s">
+      <c r="BM2" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="BK2" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL2" s="13" t="s">
+      <c r="BN2" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="BM2" s="32" t="s">
+      <c r="BO2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="BN2" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP2" s="13" t="s">
-        <v>109</v>
-      </c>
       <c r="BQ2" s="13">
-        <f t="array" ref="BQ2:BQ3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>87049</v>
+        <f t="array" aca="1" ref="BQ2:BQ3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
+        <v>19628</v>
       </c>
       <c r="BR2" s="17">
         <v>44562</v>
@@ -1410,227 +1426,226 @@
         <v>44562</v>
       </c>
       <c r="BU2" s="22">
-        <f t="shared" ref="BU2:BU3" si="5">TODAY()+365</f>
-        <v>46175</v>
+        <f t="shared" ref="BU2:BU3" ca="1" si="5">TODAY()+365</f>
+        <v>46182</v>
       </c>
       <c r="BV2" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="3" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="E3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="G3" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="H3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>45810</v>
+      </c>
+      <c r="L3" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="I3" s="16" t="s">
+      <c r="M3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="N3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="17">
-        <f t="shared" si="0"/>
-        <v>45803</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="N3" s="18" t="s">
-        <v>81</v>
-      </c>
       <c r="O3" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P3" s="16">
         <v>1542</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R3" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="U3" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>45786</v>
+      </c>
+      <c r="V3" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="S3" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="U3" s="22">
-        <f t="shared" si="1"/>
-        <v>45779</v>
-      </c>
-      <c r="V3" s="16" t="s">
+      <c r="W3" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="X3" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W3" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" s="24" t="s">
+      <c r="Y3" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z3" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y3" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z3" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA3" s="25">
         <v>795</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC3" s="26">
         <v>40</v>
       </c>
       <c r="AD3" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE3" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG3" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE3" s="19" t="s">
+      <c r="AH3" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF3" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG3" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH3" s="16" t="s">
+      <c r="AI3" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ3" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45786</v>
+      </c>
+      <c r="AK3" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45786</v>
+      </c>
+      <c r="AL3" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45786</v>
+      </c>
+      <c r="AM3" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v>N/A</v>
+      </c>
+      <c r="AN3" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO3" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="AP3" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="AI3" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ3" s="17">
-        <f t="shared" si="2"/>
-        <v>45779</v>
-      </c>
-      <c r="AK3" s="17">
-        <f t="shared" si="2"/>
-        <v>45779</v>
-      </c>
-      <c r="AL3" s="17">
-        <f t="shared" si="2"/>
-        <v>45779</v>
-      </c>
-      <c r="AM3" s="22">
-        <f t="shared" si="3"/>
-        <v>NaN</v>
-      </c>
-      <c r="AN3" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="AO3" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="AP3" s="24" t="s">
+      <c r="AQ3" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR3" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="AQ3" s="24" t="s">
+      <c r="AS3" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT3" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU3" s="17">
+        <f t="shared" ca="1" si="4"/>
+        <v>45824</v>
+      </c>
+      <c r="AV3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW3" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="AR3" s="19" t="s">
+      <c r="AX3" s="30">
+        <f ca="1"/>
+        <v>5060491932192</v>
+      </c>
+      <c r="AY3" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AS3" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT3" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU3" s="17">
-        <f t="shared" si="4"/>
-        <v>45817</v>
-      </c>
-      <c r="AV3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW3" s="29" t="s">
+      <c r="AZ3" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AX3" s="30">
-        <v>7964564254808</v>
-      </c>
-      <c r="AY3" s="17" t="s">
+      <c r="BA3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB3" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="AZ3" s="17" t="s">
+      <c r="BC3" s="30">
+        <f ca="1"/>
+        <v>83725859</v>
+      </c>
+      <c r="BD3" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BE3" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="BA3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB3" s="29" t="s">
+      <c r="BF3" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="BC3" s="30">
-        <v>76302130</v>
-      </c>
-      <c r="BD3" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE3" s="17" t="s">
+      <c r="BG3" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BH3" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BI3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ3" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BG3" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BH3" s="13" t="s">
+      <c r="BK3" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL3" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BI3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ3" s="13" t="s">
+      <c r="BM3" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="BK3" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL3" s="13" t="s">
+      <c r="BN3" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="BM3" s="32" t="s">
+      <c r="BO3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP3" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="BN3" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP3" s="13" t="s">
-        <v>109</v>
-      </c>
       <c r="BQ3" s="13">
-        <v>18270</v>
+        <f ca="1"/>
+        <v>61591</v>
       </c>
       <c r="BR3" s="17">
         <v>44562</v>
@@ -1642,40 +1657,25 @@
         <v>44562</v>
       </c>
       <c r="BU3" s="22">
-        <f t="shared" si="5"/>
-        <v>46175</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46182</v>
       </c>
       <c r="BV3" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH3 V2:V3 T2:T3 Q2:Q3 J2:J3 BL2:BL3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1"/>
-    <hyperlink ref="S3" r:id="rId2"/>
+    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
@@ -1,35 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{BB2F1E8F-AB75-4EA2-85C3-7C1C0F36ABDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="120">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -244,16 +229,22 @@
     <t>Test1</t>
   </si>
   <si>
+    <t>10699750</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>795 Store Management (Zogop Dogegy (On Leave) (10185858))</t>
   </si>
   <si>
     <t>Slovenia</t>
   </si>
   <si>
-    <t>Treva</t>
-  </si>
-  <si>
-    <t>Rodriguez</t>
+    <t>Angelica</t>
+  </si>
+  <si>
+    <t>Nolan</t>
   </si>
   <si>
     <t xml:space="preserve">070-417-626 </t>
@@ -280,7 +271,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 56587565</t>
+    <t>Auto 4373269</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -361,13 +352,16 @@
     <t>Test2</t>
   </si>
   <si>
+    <t>10699751</t>
+  </si>
+  <si>
     <t>795 Recruitment (Zosig Depazi (10280602))</t>
   </si>
   <si>
-    <t>Reece</t>
-  </si>
-  <si>
-    <t>Hahn</t>
+    <t>Lavon</t>
+  </si>
+  <si>
+    <t>West</t>
   </si>
   <si>
     <t>No</t>
@@ -385,58 +379,58 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -448,19 +442,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,27 +485,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -522,9 +504,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -902,9 +882,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BV3"/>
-  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
@@ -978,7 +958,7 @@
     <col min="74" max="74" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:74" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1202,219 +1182,223 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
+      <c r="B2" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>72</v>
+      </c>
       <c r="D2" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="17">
+        <f t="shared" ref="K2:K3" si="0">TODAY()-7</f>
+        <v>45819</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K2" s="17">
-        <f t="shared" ref="K2:K3" ca="1" si="0">TODAY()-7</f>
-        <v>45810</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>72</v>
-      </c>
       <c r="M2" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N2" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O2" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P2" s="16">
         <v>1542</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R2" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S2" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U2" s="22">
-        <f t="shared" ref="U2:U3" ca="1" si="1">TODAY()-31</f>
-        <v>45786</v>
+        <f t="shared" ref="U2:U3" si="1">TODAY()-31</f>
+        <v>45795</v>
       </c>
       <c r="V2" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W2" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="X2" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y2" s="24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Z2" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA2" s="25">
         <v>795</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC2" s="26">
         <v>40</v>
       </c>
       <c r="AD2" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE2" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF2" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG2" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH2" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI2" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AH2" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI2" s="16" t="s">
-        <v>88</v>
-      </c>
       <c r="AJ2" s="17">
-        <f t="shared" ref="AJ2:AL3" ca="1" si="2">TODAY()-31</f>
-        <v>45786</v>
+        <f t="shared" ref="AJ2:AL3" si="2">TODAY()-31</f>
+        <v>45795</v>
       </c>
       <c r="AK2" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45786</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="AL2" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45786</v>
-      </c>
-      <c r="AM2" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>45795</v>
+      </c>
+      <c r="AM2" s="22">
         <f t="shared" ref="AM2:AM3" si="3">AF2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AN2" s="16">
         <v>92</v>
       </c>
       <c r="AO2" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AP2" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AQ2" s="24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR2" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AS2" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT2" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU2" s="17">
-        <f t="shared" ref="AU2:AU3" ca="1" si="4">TODAY()+7</f>
-        <v>45824</v>
+        <f t="shared" ref="AU2:AU3" si="4">TODAY()+7</f>
+        <v>45833</v>
       </c>
       <c r="AV2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW2" s="29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AX2" s="30">
-        <f t="array" aca="1" ref="AX2:AX3" ca="1">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
-        <v>8140712665871</v>
+        <f t="array" ref="AX2:AX3">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
+        <v>7817184589616</v>
       </c>
       <c r="AY2" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AZ2" s="17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BA2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB2" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC2" s="30">
+        <f t="array" ref="BC2:BC3">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
+        <v>71879008</v>
+      </c>
+      <c r="BD2" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BC2" s="30">
-        <f t="array" aca="1" ref="BC2:BC3" ca="1">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
-        <v>33531089</v>
-      </c>
-      <c r="BD2" s="17" t="s">
-        <v>97</v>
-      </c>
       <c r="BE2" s="17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BF2" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BG2" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BH2" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BI2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ2" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BK2" s="31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL2" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BM2" s="32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BN2" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BO2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP2" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BQ2" s="13">
-        <f t="array" aca="1" ref="BQ2:BQ3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>19628</v>
+        <f t="array" ref="BQ2:BQ3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
+        <v>77682</v>
       </c>
       <c r="BR2" s="17">
         <v>44562</v>
@@ -1426,226 +1410,227 @@
         <v>44562</v>
       </c>
       <c r="BU2" s="22">
-        <f t="shared" ref="BU2:BU3" ca="1" si="5">TODAY()+365</f>
-        <v>46182</v>
+        <f t="shared" ref="BU2:BU3" si="5">TODAY()+365</f>
+        <v>46191</v>
       </c>
       <c r="BV2" s="16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="11"/>
+        <v>111</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>72</v>
+      </c>
       <c r="D3" s="12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K3" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>45810</v>
+        <f t="shared" si="0"/>
+        <v>45819</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P3" s="16">
         <v>1542</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R3" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U3" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>45786</v>
+        <f t="shared" si="1"/>
+        <v>45795</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W3" s="23" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="X3" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y3" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Z3" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA3" s="25">
         <v>795</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC3" s="26">
         <v>40</v>
       </c>
       <c r="AD3" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE3" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF3" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG3" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH3" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI3" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AH3" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI3" s="16" t="s">
-        <v>88</v>
-      </c>
       <c r="AJ3" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45786</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="AK3" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45786</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="AL3" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45786</v>
-      </c>
-      <c r="AM3" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>45795</v>
+      </c>
+      <c r="AM3" s="22">
         <f t="shared" si="3"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AN3" s="16" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AO3" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AP3" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AQ3" s="24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR3" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT3" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU3" s="17">
-        <f t="shared" ca="1" si="4"/>
-        <v>45824</v>
+        <f t="shared" si="4"/>
+        <v>45833</v>
       </c>
       <c r="AV3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW3" s="29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AX3" s="30">
-        <f ca="1"/>
-        <v>5060491932192</v>
+        <v>6958365215107</v>
       </c>
       <c r="AY3" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AZ3" s="17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BA3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB3" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC3" s="30">
+        <v>90298353</v>
+      </c>
+      <c r="BD3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BC3" s="30">
-        <f ca="1"/>
-        <v>83725859</v>
-      </c>
-      <c r="BD3" s="17" t="s">
-        <v>97</v>
-      </c>
       <c r="BE3" s="17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BF3" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BG3" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BH3" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BI3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ3" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BK3" s="31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL3" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BM3" s="32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BN3" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BO3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP3" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BQ3" s="13">
-        <f ca="1"/>
-        <v>61591</v>
+        <v>56199</v>
       </c>
       <c r="BR3" s="17">
         <v>44562</v>
@@ -1657,25 +1642,40 @@
         <v>44562</v>
       </c>
       <c r="BU3" s="22">
-        <f t="shared" ca="1" si="5"/>
-        <v>46182</v>
+        <f t="shared" si="5"/>
+        <v>46191</v>
       </c>
       <c r="BV3" s="16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH3 V2:V3 T2:T3 Q2:Q3 J2:J3 BL2:BL3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="S2" r:id="rId1"/>
+    <hyperlink ref="S3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Slovenia_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{CC840D11-CECC-4DE2-A475-86C2EFC2E162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{A92A0B85-DD8D-4D5F-96CC-4E67259C04F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -250,10 +250,10 @@
     <t>Slovenia</t>
   </si>
   <si>
-    <t>Lizeth</t>
-  </si>
-  <si>
-    <t>Renner</t>
+    <t>Santino</t>
+  </si>
+  <si>
+    <t>Jaskolski-Ondricka</t>
   </si>
   <si>
     <t xml:space="preserve">070-417-626 </t>
@@ -280,7 +280,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 87967676</t>
+    <t>Auto 91011208</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -364,10 +364,10 @@
     <t>795 Recruitment (Zosig Depazi (10280602))</t>
   </si>
   <si>
-    <t>Waino</t>
-  </si>
-  <si>
-    <t>Connelly-Cronin</t>
+    <t>Eloisa</t>
+  </si>
+  <si>
+    <t>Koch</t>
   </si>
   <si>
     <t>No</t>
@@ -1214,7 +1214,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="10">
-        <v>10700261</v>
+        <v>10700461</v>
       </c>
       <c r="C2" s="33" t="s">
         <v>117</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="K2" s="16">
         <f t="shared" ref="K2:K3" ca="1" si="0">TODAY()-7</f>
-        <v>45846</v>
+        <v>45867</v>
       </c>
       <c r="L2" s="12" t="s">
         <v>72</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="U2" s="21">
         <f t="shared" ref="U2:U3" ca="1" si="1">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="V2" s="15" t="s">
         <v>82</v>
@@ -1319,15 +1319,15 @@
       </c>
       <c r="AJ2" s="16">
         <f t="shared" ref="AJ2:AL3" ca="1" si="2">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AK2" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AL2" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AM2" s="21" t="str">
         <f t="shared" ref="AM2:AM3" si="3">AF2</f>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AU2" s="16">
         <f t="shared" ref="AU2:AU3" ca="1" si="4">TODAY()+7</f>
-        <v>45860</v>
+        <v>45881</v>
       </c>
       <c r="AV2" s="12" t="s">
         <v>72</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="AX2" s="29">
         <f t="array" aca="1" ref="AX2:AX3" ca="1">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
-        <v>4508834923209</v>
+        <v>4859642532813</v>
       </c>
       <c r="AY2" s="16" t="s">
         <v>97</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="BC2" s="29">
         <f t="array" aca="1" ref="BC2:BC3" ca="1">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
-        <v>40861965</v>
+        <v>57637609</v>
       </c>
       <c r="BD2" s="16" t="s">
         <v>97</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="BQ2" s="32">
         <f t="array" aca="1" ref="BQ2:BQ3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>97503</v>
+        <v>33569</v>
       </c>
       <c r="BR2" s="16">
         <v>44562</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="BU2" s="21">
         <f t="shared" ref="BU2:BU3" ca="1" si="5">TODAY()+365</f>
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="BV2" s="15" t="s">
         <v>108</v>
@@ -1449,7 +1449,7 @@
         <v>109</v>
       </c>
       <c r="B3" s="10">
-        <v>10700262</v>
+        <v>10700462</v>
       </c>
       <c r="C3" s="33" t="s">
         <v>117</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="K3" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>45846</v>
+        <v>45867</v>
       </c>
       <c r="L3" s="12" t="s">
         <v>72</v>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="U3" s="21">
         <f t="shared" ca="1" si="1"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="V3" s="15" t="s">
         <v>82</v>
@@ -1554,15 +1554,15 @@
       </c>
       <c r="AJ3" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AK3" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AL3" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AM3" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="AU3" s="16">
         <f t="shared" ca="1" si="4"/>
-        <v>45860</v>
+        <v>45881</v>
       </c>
       <c r="AV3" s="12" t="s">
         <v>72</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AX3" s="29">
         <f ca="1"/>
-        <v>6021367736358</v>
+        <v>5082630747872</v>
       </c>
       <c r="AY3" s="16" t="s">
         <v>97</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="BC3" s="29">
         <f ca="1"/>
-        <v>54526600</v>
+        <v>14255899</v>
       </c>
       <c r="BD3" s="16" t="s">
         <v>97</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="BQ3" s="32">
         <f ca="1"/>
-        <v>58668</v>
+        <v>68169</v>
       </c>
       <c r="BR3" s="16">
         <v>44562</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="BU3" s="21">
         <f t="shared" ca="1" si="5"/>
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="BV3" s="15" t="s">
         <v>108</v>
